--- a/crl_summary_results.xlsx
+++ b/crl_summary_results.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="ConstrainedGoToLocal_1c" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="ConstrainedGoToOpen_1c" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ConstrainedOpenDoorsOrder_1c" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -928,4 +929,263 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Constraint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>287.89 ± 347.09</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.09</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>270.79 ± 333.88</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>764.97 ± 450.76</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>36.68 ± 44.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>285.36 ± 353.21</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>289.70 ± 366.24</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>743.23 ± 462.60</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>35.48 ± 42.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>318.79 ± 392.38</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.14 ± 1.76</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>264.42 ± 332.25</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.13</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>741.68 ± 455.09</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>34.88 ± 44.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>318.94 ± 378.23</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.29</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>281.30 ± 351.03</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.58</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>765.21 ± 458.64</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>35.62 ± 40.94</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crl_summary_results.xlsx
+++ b/crl_summary_results.xlsx
@@ -10,6 +10,7 @@
     <sheet name="ConstrainedGoToLocal_1c" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="ConstrainedGoToOpen_1c" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ConstrainedOpenDoorsOrder_1c" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ConstrainedOpenDoorLoc_1c" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1188,4 +1189,263 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Constraint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>176.60 ± 235.25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.14</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>444.23 ± 383.48</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>7.35 ± 30.39</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>567.56 ± 290.97</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>24.33 ± 28.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>181.33 ± 234.14</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.27</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>494.16 ± 373.50</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6.03 ± 26.65</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>574.53 ± 286.23</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>27.36 ± 34.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>490.10 ± 372.35</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3.37 ± 12.87</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>480.90 ± 379.46</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5.36 ± 23.51</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>551.86 ± 297.27</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>24.11 ± 31.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>477.27 ± 375.55</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3.54 ± 13.07</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>459.19 ± 379.66</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7.91 ± 37.13</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>563.30 ± 292.96</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>23.84 ± 32.89</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crl_summary_results.xlsx
+++ b/crl_summary_results.xlsx
@@ -7,10 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ConstrainedGoToLocal_1c" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ConstrainedGoToOpen_1c" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ConstrainedOpenDoorsOrder_1c" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ConstrainedOpenDoorLoc_1c" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ConstrainedGoToObjDoor_1c" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ConstrainedGoToLocal_1c" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ConstrainedActionObjDoor_1c" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ConstrainedOpenDoor_1c" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ConstrainedOpenDoorsOrder_1c" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ConstrainedOpenDoorLoc_1c" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ConstrainedPickupDist_1c" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ConstrainedGoToOpen_1c" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,61 +424,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Delta Theta</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Delta Constraint</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Success Prob C-LAMAML</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps CRL</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success Prob CRL</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols CRL</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Avg Steps Random</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Success Prob Random</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Viols Random</t>
         </is>
@@ -489,41 +493,41 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23.33 ± 22.43</t>
+          <t>87.09 ± 92.70</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>0.00 ± 0.09</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>79.18 ± 85.66</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>62.00 ± 106.78</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>240.83 ± 107.36</t>
+          <t>196.25 ± 113.90</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.33</v>
+        <v>0.55</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>33.83 ± 28.84</t>
+          <t>10.69 ± 19.66</t>
         </is>
       </c>
     </row>
@@ -536,11 +540,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>84.33 ± 102.96</t>
+          <t>80.41 ± 90.03</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -549,11 +553,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>114.67 ± 98.93</t>
+          <t>77.77 ± 87.11</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -562,15 +566,15 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>226.00 ± 105.59</t>
+          <t>205.66 ± 107.69</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>21.00 ± 22.70</t>
+          <t>12.17 ± 20.85</t>
         </is>
       </c>
     </row>
@@ -583,41 +587,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>93.33 ± 107.89</t>
+          <t>88.38 ± 92.73</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>0.01 ± 0.09</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>83.66 ± 88.24</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>47.50 ± 44.88</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>196.17 ± 109.66</t>
+          <t>214.23 ± 106.05</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>21.67 ± 39.91</t>
+          <t>11.05 ± 16.11</t>
         </is>
       </c>
     </row>
@@ -630,41 +634,88 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>123.00 ± 126.61</t>
+          <t>86.07 ± 91.73</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.67</v>
+        <v>0.91</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>0.01 ± 0.18</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>76.83 ± 83.62</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>185.83 ± 93.76</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>210.88 ± 109.84</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>11.74 ± 18.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>95.42 ± 99.80</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>243.33 ± 104.07</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>6.83 ± 9.75</t>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>82.55 ± 86.56</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>202.85 ± 113.18</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>11.22 ± 18.16</t>
         </is>
       </c>
     </row>
@@ -679,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,41 +799,41 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>559.12 ± 437.86</t>
+          <t>87.80 ± 106.44</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.57</v>
+        <v>0.84</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8.62 ± 29.14</t>
+          <t>0.02 ± 0.45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>569.32 ± 440.12</t>
+          <t>86.27 ± 104.48</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>201.11 ± 109.77</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>0.54</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>9.90 ± 41.16</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>704.68 ± 395.68</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.42</v>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>19.58 ± 47.30</t>
+          <t>21.30 ± 30.24</t>
         </is>
       </c>
     </row>
@@ -795,41 +846,41 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>441.91 ± 423.16</t>
+          <t>87.30 ± 106.30</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.65 ± 33.21</t>
+          <t>0.04 ± 0.80</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>568.42 ± 453.86</t>
+          <t>88.05 ± 100.88</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.51</v>
+        <v>0.88</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>13.98 ± 56.09</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>686.70 ± 408.00</t>
+          <t>204.18 ± 109.04</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>13.81 ± 37.57</t>
+          <t>21.05 ± 29.40</t>
         </is>
       </c>
     </row>
@@ -842,41 +893,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>496.79 ± 438.08</t>
+          <t>91.39 ± 110.34</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.62</v>
+        <v>0.83</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.34 ± 21.33</t>
+          <t>0.00 ± 0.04</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>535.49 ± 458.11</t>
+          <t>91.89 ± 111.19</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>201.60 ± 110.33</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>0.54</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>10.17 ± 34.73</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>709.83 ± 393.85</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.4</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>21.58 ± 50.41</t>
+          <t>19.64 ± 26.59</t>
         </is>
       </c>
     </row>
@@ -889,41 +940,88 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>481.30 ± 437.59</t>
+          <t>88.64 ± 103.33</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.64</v>
+        <v>0.87</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.08 ± 16.67</t>
+          <t>0.01 ± 0.21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>534.87 ± 450.64</t>
+          <t>97.23 ± 112.32</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.57</v>
+        <v>0.82</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9.16 ± 40.15</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>689.76 ± 393.46</t>
+          <t>206.35 ± 105.18</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.44</v>
+        <v>0.55</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>17.80 ± 45.42</t>
+          <t>20.78 ± 27.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>84.80 ± 101.95</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.27</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>84.80 ± 103.98</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>202.29 ± 108.26</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>19.42 ± 26.84</t>
         </is>
       </c>
     </row>
@@ -938,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1007,24 +1105,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>287.89 ± 347.09</t>
+          <t>461.61 ± 433.09</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.93</v>
+        <v>0.64</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.00 ± 0.09</t>
+          <t>0.38 ± 1.21</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>270.79 ± 333.88</t>
+          <t>611.90 ± 435.91</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1033,15 +1131,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>764.97 ± 450.76</t>
+          <t>640.91 ± 401.86</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>36.68 ± 44.64</t>
+          <t>25.86 ± 30.09</t>
         </is>
       </c>
     </row>
@@ -1054,24 +1152,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>285.36 ± 353.21</t>
+          <t>487.47 ± 429.77</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.02 ± 0.20</t>
+          <t>2.13 ± 6.56</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>289.70 ± 366.24</t>
+          <t>560.93 ± 445.22</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.91</v>
+        <v>0.53</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1080,15 +1178,15 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>743.23 ± 462.60</t>
+          <t>642.07 ± 404.36</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>35.48 ± 42.72</t>
+          <t>28.70 ± 41.46</t>
         </is>
       </c>
     </row>
@@ -1101,41 +1199,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>318.79 ± 392.38</t>
+          <t>352.79 ± 397.57</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.89</v>
+        <v>0.76</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.14 ± 1.76</t>
+          <t>0.23 ± 1.04</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>264.42 ± 332.25</t>
+          <t>603.31 ± 441.83</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.01 ± 0.13</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>741.68 ± 455.09</t>
+          <t>715.37 ± 385.32</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.6</v>
+        <v>0.41</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>34.88 ± 44.11</t>
+          <t>32.13 ± 41.14</t>
         </is>
       </c>
     </row>
@@ -1148,41 +1246,88 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>318.94 ± 378.23</t>
+          <t>468.26 ± 431.94</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.02 ± 0.29</t>
+          <t>0.47 ± 1.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>281.30 ± 351.03</t>
+          <t>603.13 ± 437.07</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.93</v>
+        <v>0.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.03 ± 0.58</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>765.21 ± 458.64</t>
+          <t>681.11 ± 397.59</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>35.62 ± 40.94</t>
+          <t>23.15 ± 32.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>508.25 ± 444.10</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2.94 ± 8.52</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>560.17 ± 444.55</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>723.22 ± 380.78</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>26.51 ± 31.90</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,41 +1411,41 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>176.60 ± 235.25</t>
+          <t>232.83 ± 247.06</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.01 ± 0.14</t>
+          <t>0.01 ± 0.18</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>444.23 ± 383.48</t>
+          <t>219.03 ± 248.80</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.47</v>
+        <v>0.9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7.35 ± 30.39</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>567.56 ± 290.97</t>
+          <t>624.73 ± 269.64</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>24.33 ± 28.96</t>
+          <t>20.27 ± 24.86</t>
         </is>
       </c>
     </row>
@@ -1313,41 +1458,41 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>181.33 ± 234.14</t>
+          <t>343.90 ± 335.62</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.92</v>
+        <v>0.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.02 ± 0.27</t>
+          <t>0.72 ± 4.28</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>494.16 ± 373.50</t>
+          <t>245.50 ± 263.02</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.41</v>
+        <v>0.88</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.03 ± 26.65</t>
+          <t>0.04 ± 0.43</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>574.53 ± 286.23</t>
+          <t>616.70 ± 274.58</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>27.36 ± 34.41</t>
+          <t>25.94 ± 34.47</t>
         </is>
       </c>
     </row>
@@ -1360,6 +1505,618 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>230.74 ± 258.11</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.14 ± 1.12</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>231.61 ± 248.88</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.14</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>561.87 ± 297.68</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>23.89 ± 31.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>374.14 ± 343.08</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.09 ± 4.26</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>229.38 ± 248.98</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.06</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>607.80 ± 278.23</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>24.84 ± 29.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>423.98 ± 347.67</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3.71 ± 9.30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>214.99 ± 252.87</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.23</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>629.21 ± 259.30</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>21.23 ± 26.50</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Constraint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>287.89 ± 347.09</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.09</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>270.79 ± 333.88</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>756.98 ± 444.96</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>33.05 ± 35.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>285.36 ± 353.21</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>289.70 ± 366.24</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>736.97 ± 462.07</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>36.89 ± 44.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>318.79 ± 392.38</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.14 ± 1.76</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>264.42 ± 332.25</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.13</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>748.72 ± 470.45</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>33.98 ± 42.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>318.94 ± 378.23</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.29</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>281.30 ± 351.03</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.58</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>749.27 ± 454.69</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>37.38 ± 46.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>335.32 ± 389.14</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.06 ± 0.39</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>269.16 ± 329.96</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.37</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>762.33 ± 454.42</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>37.76 ± 46.05</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Constraint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>176.60 ± 235.25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.14</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>444.23 ± 383.48</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>7.35 ± 30.39</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>579.18 ± 286.25</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>25.17 ± 35.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>181.33 ± 234.14</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.27</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>494.16 ± 373.50</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6.03 ± 26.65</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>579.27 ± 284.26</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>25.65 ± 35.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>490.10 ± 372.35</t>
         </is>
       </c>
@@ -1386,15 +2143,15 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>551.86 ± 297.27</t>
+          <t>598.85 ± 274.82</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.49</v>
+        <v>0.43</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>24.11 ± 31.71</t>
+          <t>27.80 ± 37.15</t>
         </is>
       </c>
     </row>
@@ -1433,15 +2190,674 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>563.30 ± 292.96</t>
+          <t>578.15 ± 289.99</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>23.84 ± 32.89</t>
+          <t>24.50 ± 29.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>474.96 ± 375.21</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4.66 ± 16.50</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>441.15 ± 382.52</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6.50 ± 27.33</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>575.47 ± 288.60</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>23.42 ± 28.07</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Constraint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>321.50 ± 200.42</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.13</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>260.99 ± 200.54</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>422.47 ± 149.32</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>23.67 ± 30.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>286.53 ± 202.34</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.12</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>279.28 ± 200.19</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>415.45 ± 154.60</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>24.82 ± 31.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>275.24 ± 197.92</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.12 ± 1.28</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>256.55 ± 200.04</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>422.32 ± 152.87</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>23.39 ± 30.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>240.93 ± 191.10</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>269.46 ± 202.72</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>405.94 ± 165.22</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>24.70 ± 34.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>273.29 ± 200.00</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.13 ± 1.17</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>267.21 ± 197.56</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>415.45 ± 157.49</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>24.32 ± 34.14</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Constraint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>559.12 ± 437.86</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8.62 ± 29.14</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>569.32 ± 440.12</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9.90 ± 41.16</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>708.27 ± 391.21</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>19.75 ± 42.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>441.91 ± 423.16</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5.65 ± 33.21</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>568.42 ± 453.86</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>13.98 ± 56.09</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>692.97 ± 401.09</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>15.39 ± 38.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>496.79 ± 438.08</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5.34 ± 21.33</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>535.49 ± 458.11</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>10.17 ± 34.73</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>700.53 ± 397.05</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>18.25 ± 44.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>481.30 ± 437.59</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4.08 ± 16.67</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>534.87 ± 450.64</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>9.16 ± 40.15</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>689.33 ± 395.59</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>18.08 ± 43.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>538.58 ± 438.13</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7.57 ± 25.40</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>548.35 ± 448.85</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7.37 ± 25.40</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>713.79 ± 387.75</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>17.95 ± 43.83</t>
         </is>
       </c>
     </row>

--- a/crl_summary_results.xlsx
+++ b/crl_summary_results.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ConstrainedGoToObjDoor_1c" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ConstrainedGoToLocal_1c" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ConstrainedGoToLocal_1c" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ConstrainedGoToObjDoor_1c" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ConstrainedActionObjDoor_1c" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ConstrainedOpenDoor_1c" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="ConstrainedOpenDoorsOrder_1c" sheetId="5" state="visible" r:id="rId5"/>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,24 +493,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>87.09 ± 92.70</t>
+          <t>87.80 ± 106.44</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.00 ± 0.09</t>
+          <t>0.02 ± 0.45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>79.18 ± 85.66</t>
+          <t>86.27 ± 104.48</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -519,7 +519,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>196.25 ± 113.90</t>
+          <t>203.28 ± 108.07</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -527,7 +527,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>10.69 ± 19.66</t>
+          <t>20.77 ± 26.45</t>
         </is>
       </c>
     </row>
@@ -540,33 +540,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>80.41 ± 90.03</t>
+          <t>87.30 ± 106.30</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>0.04 ± 0.80</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>88.05 ± 100.88</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>77.77 ± 87.11</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>205.66 ± 107.69</t>
+          <t>203.19 ± 109.33</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -574,37 +574,37 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>12.17 ± 20.85</t>
+          <t>19.85 ± 28.81</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="B4" t="n">
         <v>0.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>88.38 ± 92.73</t>
+          <t>82.70 ± 102.90</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.01 ± 0.09</t>
+          <t>0.06 ± 0.85</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>83.66 ± 88.24</t>
+          <t>83.80 ± 105.83</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.93</v>
+        <v>0.84</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -613,45 +613,45 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>214.23 ± 106.05</t>
+          <t>195.04 ± 111.72</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.49</v>
+        <v>0.57</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>11.05 ± 16.11</t>
+          <t>20.53 ± 28.45</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>86.07 ± 91.73</t>
+          <t>91.74 ± 104.91</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.01 ± 0.18</t>
+          <t>0.02 ± 0.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>76.83 ± 83.62</t>
+          <t>93.43 ± 109.62</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -660,62 +660,250 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>210.88 ± 109.84</t>
+          <t>203.45 ± 109.39</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>11.74 ± 18.71</t>
+          <t>21.71 ± 31.67</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>89.26 ± 105.98</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.67</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>82.89 ± 101.98</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.26</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>202.88 ± 111.70</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>21.90 ± 31.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>85.26 ± 103.59</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.06 ± 1.35</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>82.27 ± 100.62</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>198.58 ± 110.43</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>19.39 ± 27.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>84.02 ± 99.62</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>90.40 ± 106.33</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.08</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>205.23 ± 104.76</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>20.09 ± 26.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>82.02 ± 97.33</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.44</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>82.92 ± 104.55</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.44</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>201.71 ± 107.57</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>20.52 ± 29.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>95.42 ± 99.80</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>82.41 ± 101.75</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.15</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>77.56 ± 98.53</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>82.55 ± 86.56</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>202.85 ± 113.18</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>11.22 ± 18.16</t>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>199.59 ± 110.37</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>18.36 ± 25.24</t>
         </is>
       </c>
     </row>
@@ -730,7 +918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,24 +987,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>87.80 ± 106.44</t>
+          <t>87.09 ± 92.70</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.02 ± 0.45</t>
+          <t>0.00 ± 0.09</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>86.27 ± 104.48</t>
+          <t>79.18 ± 85.66</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -825,15 +1013,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>201.11 ± 109.77</t>
+          <t>207.48 ± 110.94</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>21.30 ± 30.24</t>
+          <t>12.77 ± 20.00</t>
         </is>
       </c>
     </row>
@@ -846,24 +1034,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>87.30 ± 106.30</t>
+          <t>80.41 ± 90.03</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.04 ± 0.80</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>88.05 ± 100.88</t>
+          <t>77.77 ± 87.11</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -872,45 +1060,45 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>204.18 ± 109.04</t>
+          <t>212.70 ± 105.60</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>21.05 ± 29.40</t>
+          <t>11.78 ± 20.09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="B4" t="n">
         <v>0.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>91.39 ± 110.34</t>
+          <t>82.65 ± 87.73</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.00 ± 0.04</t>
+          <t>0.00 ± 0.09</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>91.89 ± 111.19</t>
+          <t>83.33 ± 89.26</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -919,45 +1107,45 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>201.60 ± 110.33</t>
+          <t>208.07 ± 109.15</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>19.64 ± 26.59</t>
+          <t>10.95 ± 18.56</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>88.64 ± 103.33</t>
+          <t>87.83 ± 89.85</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.01 ± 0.21</t>
+          <t>0.01 ± 0.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>97.23 ± 112.32</t>
+          <t>88.48 ± 89.85</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -966,62 +1154,250 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>206.35 ± 105.18</t>
+          <t>207.05 ± 110.16</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20.78 ± 27.80</t>
+          <t>12.36 ± 20.26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>91.38 ± 97.57</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.06</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>79.23 ± 87.00</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>198.62 ± 111.39</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>11.13 ± 18.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>94.04 ± 94.60</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>78.00 ± 85.46</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>204.07 ± 108.46</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>10.69 ± 17.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>93.13 ± 97.30</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.09</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>84.71 ± 86.76</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>209.76 ± 109.58</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>12.94 ± 21.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>99.34 ± 105.20</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>80.55 ± 86.54</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>206.10 ± 113.30</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>11.23 ± 18.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>84.80 ± 101.95</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.03 ± 0.27</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>84.80 ± 103.98</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>97.52 ± 99.07</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.33</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>81.12 ± 85.47</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>202.29 ± 108.26</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>19.42 ± 26.84</t>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>208.29 ± 111.17</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>10.39 ± 17.37</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,15 +1507,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>640.91 ± 401.86</t>
+          <t>756.06 ± 366.08</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.48</v>
+        <v>0.35</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>25.86 ± 30.09</t>
+          <t>29.78 ± 34.67</t>
         </is>
       </c>
     </row>
@@ -1178,41 +1554,41 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>642.07 ± 404.36</t>
+          <t>724.05 ± 372.71</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>28.70 ± 41.46</t>
+          <t>26.96 ± 36.54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="B4" t="n">
         <v>0.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>352.79 ± 397.57</t>
+          <t>525.83 ± 450.09</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.76</v>
+        <v>0.55</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.23 ± 1.04</t>
+          <t>0.53 ± 1.98</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>603.31 ± 441.83</t>
+          <t>606.88 ± 436.62</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1225,109 +1601,297 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>715.37 ± 385.32</t>
+          <t>711.12 ± 374.00</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>32.13 ± 41.14</t>
+          <t>29.66 ± 38.75</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>380.03 ± 399.58</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.68 ± 1.67</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>586.34 ± 451.43</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>634.66 ± 401.70</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>0.5</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>468.26 ± 431.94</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.47 ± 1.55</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>603.13 ± 437.07</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>681.11 ± 397.59</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.43</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>23.15 ± 32.84</t>
+          <t>28.54 ± 34.97</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>360.28 ± 364.82</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.32 ± 1.19</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>550.48 ± 444.75</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>707.19 ± 382.96</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>28.89 ± 34.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>469.20 ± 427.05</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.41 ± 3.63</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>572.63 ± 439.84</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.40</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>667.78 ± 417.55</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>23.68 ± 30.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>455.90 ± 431.83</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3.94 ± 8.77</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>570.73 ± 439.82</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>715.51 ± 416.47</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>26.65 ± 38.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>488.55 ± 448.06</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.85 ± 7.10</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>608.91 ± 437.89</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>699.65 ± 398.23</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>33.58 ± 46.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>508.25 ± 444.10</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2.94 ± 8.52</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>560.17 ± 444.55</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>492.56 ± 438.69</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4.07 ± 9.33</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>496.74 ± 454.13</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>723.22 ± 380.78</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>26.51 ± 31.90</t>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>667.67 ± 408.91</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>25.00 ± 33.91</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1437,15 +2001,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>624.73 ± 269.64</t>
+          <t>591.84 ± 288.52</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.36</v>
+        <v>0.41</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20.27 ± 24.86</t>
+          <t>22.74 ± 29.84</t>
         </is>
       </c>
     </row>
@@ -1484,88 +2048,88 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>616.70 ± 274.58</t>
+          <t>620.68 ± 266.85</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>25.94 ± 34.47</t>
+          <t>23.38 ± 31.48</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="B4" t="n">
         <v>0.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>230.74 ± 258.11</t>
+          <t>336.59 ± 335.33</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.14 ± 1.12</t>
+          <t>1.04 ± 6.50</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>231.61 ± 248.88</t>
+          <t>248.82 ± 247.98</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.01 ± 0.14</t>
+          <t>0.02 ± 0.29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>561.87 ± 297.68</t>
+          <t>623.29 ± 273.06</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>23.89 ± 31.23</t>
+          <t>25.86 ± 35.24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>374.14 ± 343.08</t>
+          <t>511.12 ± 353.72</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.64</v>
+        <v>0.42</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.09 ± 4.26</t>
+          <t>6.47 ± 18.56</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>229.38 ± 248.98</t>
+          <t>209.28 ± 236.30</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1573,46 +2137,46 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.00 ± 0.06</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>607.80 ± 278.23</t>
+          <t>584.04 ± 291.27</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>24.84 ± 29.53</t>
+          <t>23.46 ± 30.72</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>423.98 ± 347.67</t>
+          <t>245.51 ± 269.49</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.58</v>
+        <v>0.87</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.71 ± 9.30</t>
+          <t>0.36 ± 3.09</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>214.99 ± 252.87</t>
+          <t>233.85 ± 257.67</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1620,20 +2184,208 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>633.28 ± 269.05</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>25.78 ± 32.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>526.82 ± 344.60</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5.59 ± 20.62</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>221.61 ± 248.55</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.12</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>658.12 ± 248.87</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>26.96 ± 31.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>563.48 ± 349.21</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4.94 ± 13.47</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>238.25 ± 261.54</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>618.33 ± 270.81</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>24.16 ± 28.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>404.35 ± 357.51</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.56 ± 7.98</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>253.36 ± 260.44</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>0.01 ± 0.23</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>629.21 ± 259.30</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>633.72 ± 264.10</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>27.34 ± 31.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>395.26 ± 343.26</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4.32 ± 16.68</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>219.90 ± 252.18</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.64</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>608.13 ± 286.59</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>0.37</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>21.23 ± 26.50</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>21.19 ± 28.99</t>
         </is>
       </c>
     </row>
@@ -1648,7 +2400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1743,15 +2495,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>756.98 ± 444.96</t>
+          <t>750.65 ± 461.33</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>33.05 ± 35.72</t>
+          <t>37.16 ± 46.65</t>
         </is>
       </c>
     </row>
@@ -1790,28 +2542,28 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>736.97 ± 462.07</t>
+          <t>747.78 ± 447.11</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>36.89 ± 44.86</t>
+          <t>37.55 ± 42.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="B4" t="n">
         <v>0.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>318.79 ± 392.38</t>
+          <t>336.41 ± 379.88</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1819,93 +2571,93 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.14 ± 1.76</t>
+          <t>0.03 ± 0.59</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>264.42 ± 332.25</t>
+          <t>263.63 ± 340.20</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.01 ± 0.13</t>
+          <t>0.00 ± 0.04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>748.72 ± 470.45</t>
+          <t>733.26 ± 453.59</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>33.98 ± 42.93</t>
+          <t>34.01 ± 40.11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>318.94 ± 378.23</t>
+          <t>315.67 ± 369.81</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.02 ± 0.29</t>
+          <t>0.05 ± 0.41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>281.30 ± 351.03</t>
+          <t>290.68 ± 351.37</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.03 ± 0.58</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>749.27 ± 454.69</t>
+          <t>746.90 ± 464.19</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>37.38 ± 46.16</t>
+          <t>34.74 ± 40.86</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>335.32 ± 389.14</t>
+          <t>331.49 ± 392.96</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1913,33 +2665,221 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.06 ± 0.39</t>
+          <t>0.09 ± 0.63</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>269.16 ± 329.96</t>
+          <t>307.98 ± 367.68</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>717.78 ± 461.27</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>33.00 ± 41.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>332.28 ± 384.15</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.90</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>297.24 ± 367.88</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.36</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>773.11 ± 465.86</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>37.25 ± 43.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>331.30 ± 382.26</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.17 ± 1.25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>265.10 ± 348.70</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>0.93</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.02 ± 0.37</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>762.33 ± 454.42</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.18</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>780.91 ± 454.75</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>38.97 ± 43.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>347.18 ± 411.67</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.39</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>275.96 ± 342.49</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.27</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>743.23 ± 451.99</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>37.95 ± 43.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>361.39 ± 415.05</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.06 ± 0.49</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>277.68 ± 359.01</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.32</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>754.62 ± 447.13</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>0.58</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>37.76 ± 46.05</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>33.82 ± 41.45</t>
         </is>
       </c>
     </row>
@@ -1954,7 +2894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2049,15 +2989,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>579.18 ± 286.25</t>
+          <t>581.26 ± 284.24</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>25.17 ± 35.76</t>
+          <t>24.04 ± 30.49</t>
         </is>
       </c>
     </row>
@@ -2096,88 +3036,88 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>579.27 ± 284.26</t>
+          <t>572.01 ± 287.87</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>25.65 ± 35.41</t>
+          <t>25.48 ± 33.93</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="B4" t="n">
         <v>0.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>490.10 ± 372.35</t>
+          <t>500.19 ± 371.45</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.37 ± 12.87</t>
+          <t>2.74 ± 10.83</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>480.90 ± 379.46</t>
+          <t>472.85 ± 380.70</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.36 ± 23.51</t>
+          <t>5.32 ± 25.44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>598.85 ± 274.82</t>
+          <t>565.42 ± 293.66</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>27.80 ± 37.15</t>
+          <t>23.51 ± 34.02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>477.27 ± 375.55</t>
+          <t>273.95 ± 306.64</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.54 ± 13.07</t>
+          <t>0.92 ± 3.09</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>459.19 ± 379.66</t>
+          <t>456.82 ± 379.79</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2185,67 +3125,255 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7.91 ± 37.13</t>
+          <t>7.97 ± 39.04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>578.15 ± 289.99</t>
+          <t>568.09 ± 288.94</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>24.50 ± 29.01</t>
+          <t>24.64 ± 36.56</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>454.97 ± 378.12</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3.85 ± 13.24</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>445.89 ± 382.39</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5.19 ± 21.70</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>592.99 ± 282.35</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>24.25 ± 29.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>488.23 ± 376.11</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3.91 ± 16.47</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>473.83 ± 380.02</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8.64 ± 42.67</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>572.25 ± 289.77</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>24.08 ± 30.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>464.73 ± 375.60</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4.12 ± 17.75</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>467.99 ± 380.36</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>7.59 ± 37.65</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>578.77 ± 287.91</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>24.61 ± 33.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>311.86 ± 334.75</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2.55 ± 9.19</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>478.91 ± 377.97</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6.32 ± 34.77</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>545.23 ± 294.47</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>22.54 ± 27.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>474.96 ± 375.21</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>473.55 ± 375.80</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>0.43</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4.66 ± 16.50</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>441.15 ± 382.52</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6.04 ± 25.50</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>458.55 ± 382.14</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6.27 ± 32.53</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>557.47 ± 296.00</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>0.47</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>6.50 ± 27.33</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>575.47 ± 288.60</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>23.42 ± 28.07</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>23.69 ± 31.77</t>
         </is>
       </c>
     </row>
@@ -2260,7 +3388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2355,7 +3483,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>422.47 ± 149.32</t>
+          <t>416.86 ± 155.51</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -2363,7 +3491,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>23.67 ± 30.44</t>
+          <t>22.80 ± 29.40</t>
         </is>
       </c>
     </row>
@@ -2402,45 +3530,45 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>415.45 ± 154.60</t>
+          <t>422.85 ± 149.15</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>24.82 ± 31.74</t>
+          <t>26.64 ± 33.45</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="B4" t="n">
         <v>0.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>275.24 ± 197.92</t>
+          <t>256.66 ± 192.27</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.12 ± 1.28</t>
+          <t>0.01 ± 0.17</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>256.55 ± 200.04</t>
+          <t>254.10 ± 197.65</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2449,109 +3577,297 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>422.32 ± 152.87</t>
+          <t>407.16 ± 162.29</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>23.39 ± 30.46</t>
+          <t>24.73 ± 33.90</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>240.93 ± 191.10</t>
+          <t>267.39 ± 200.68</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>0.08 ± 0.45</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>258.34 ± 201.55</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>269.46 ± 202.72</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.04</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>405.94 ± 165.22</t>
+          <t>412.99 ± 154.13</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>24.70 ± 34.30</t>
+          <t>26.44 ± 33.32</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>270.44 ± 201.23</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.07 ± 0.70</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>267.83 ± 196.69</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>416.93 ± 154.02</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>26.17 ± 33.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>280.19 ± 195.87</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.40</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>251.65 ± 201.69</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.16</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>419.33 ± 150.92</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>27.34 ± 35.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>249.73 ± 192.79</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.07 ± 0.54</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>274.62 ± 198.12</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>418.96 ± 150.60</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>25.29 ± 31.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>263.92 ± 192.74</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.83 ± 2.97</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>253.07 ± 200.88</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.08</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>422.22 ± 148.43</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>24.96 ± 31.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>273.29 ± 200.00</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.13 ± 1.17</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>267.21 ± 197.56</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>281.74 ± 202.57</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.12 ± 0.98</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>265.59 ± 199.98</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>0.68</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>415.45 ± 157.49</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>24.32 ± 34.14</t>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>404.90 ± 160.33</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>25.67 ± 31.97</t>
         </is>
       </c>
     </row>
@@ -2566,7 +3882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2661,7 +3977,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>708.27 ± 391.21</t>
+          <t>715.55 ± 389.12</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -2669,7 +3985,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>19.75 ± 42.59</t>
+          <t>21.08 ± 52.42</t>
         </is>
       </c>
     </row>
@@ -2708,41 +4024,41 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>692.97 ± 401.09</t>
+          <t>673.97 ± 412.54</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.39 ± 38.26</t>
+          <t>16.28 ± 42.42</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="B4" t="n">
         <v>0.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>496.79 ± 438.08</t>
+          <t>491.09 ± 442.46</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.34 ± 21.33</t>
+          <t>3.71 ± 14.78</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>535.49 ± 458.11</t>
+          <t>529.45 ± 458.15</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2750,12 +4066,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10.17 ± 34.73</t>
+          <t>10.13 ± 33.99</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>700.53 ± 397.05</t>
+          <t>709.80 ± 390.06</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -2763,80 +4079,80 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>18.25 ± 44.84</t>
+          <t>20.38 ± 52.94</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>481.30 ± 437.59</t>
+          <t>469.16 ± 426.23</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.08 ± 16.67</t>
+          <t>7.91 ± 31.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>534.87 ± 450.64</t>
+          <t>534.92 ± 451.43</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9.16 ± 40.15</t>
+          <t>13.25 ± 61.39</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>689.33 ± 395.59</t>
+          <t>692.97 ± 402.19</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>18.08 ± 43.49</t>
+          <t>17.21 ± 37.10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>538.58 ± 438.13</t>
+          <t>533.89 ± 441.68</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7.57 ± 25.40</t>
+          <t>5.84 ± 21.27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>548.35 ± 448.85</t>
+          <t>556.14 ± 447.84</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2844,20 +4160,208 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7.37 ± 25.40</t>
+          <t>8.29 ± 29.73</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>713.79 ± 387.75</t>
+          <t>715.24 ± 395.43</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>17.95 ± 43.83</t>
+          <t>21.14 ± 55.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>493.30 ± 433.25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>11.35 ± 64.94</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>578.11 ± 445.75</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>15.07 ± 54.20</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>701.29 ± 406.87</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>19.14 ± 43.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>503.16 ± 430.98</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8.27 ± 52.91</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>574.61 ± 450.45</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>12.64 ± 45.46</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>677.88 ± 407.50</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>16.55 ± 41.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>474.34 ± 430.72</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8.23 ± 51.06</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>546.45 ± 455.88</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12.16 ± 43.12</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>692.92 ± 391.55</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>24.11 ± 57.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>548.50 ± 439.08</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9.19 ± 32.18</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>551.39 ± 449.00</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>14.01 ± 54.81</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>675.28 ± 409.30</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>23.43 ± 55.17</t>
         </is>
       </c>
     </row>

--- a/crl_summary_results.xlsx
+++ b/crl_summary_results.xlsx
@@ -15,6 +15,14 @@
     <sheet name="ConstrainedOpenDoorLoc_1c" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ConstrainedPickupDist_1c" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="ConstrainedGoToOpen_1c" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ConstrainedGoToLocal_2c" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="ConstrainedGoToObjDoor_2c" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="ConstrainedActionObjDoor_2c" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ConstrainedOpenDoor_2c" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ConstrainedPickupDist_2c" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ConstrainedOpenDoorsOrder_2c" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ConstrainedOpenDoorLoc_2c" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="ConstrainedGoToOpen_2c" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -912,6 +920,3135 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Constraint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>104.34 ± 107.50</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.09</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>98.69 ± 100.93</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>212.24 ± 107.41</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>20.51 ± 24.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>110.46 ± 112.03</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.24</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>97.91 ± 104.14</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>209.46 ± 109.49</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>24.58 ± 30.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>115.32 ± 110.10</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>109.91 ± 108.30</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>212.21 ± 108.10</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>22.91 ± 26.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>101.02 ± 102.81</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>96.53 ± 98.88</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>212.25 ± 108.34</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>25.41 ± 29.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>110.47 ± 113.73</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.50</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>99.75 ± 101.61</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>209.06 ± 110.45</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>22.38 ± 26.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>120.02 ± 115.97</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.11</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>95.32 ± 101.45</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>216.00 ± 108.26</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>23.19 ± 26.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>117.82 ± 115.82</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.08</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>103.03 ± 103.37</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>213.53 ± 108.23</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>24.67 ± 29.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>115.29 ± 111.07</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>105.01 ± 105.24</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>211.49 ± 109.72</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>25.40 ± 29.35</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Constraint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>480.65 ± 416.16</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.46 ± 1.43</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>650.05 ± 424.83</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>739.77 ± 369.71</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>59.74 ± 55.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>459.63 ± 433.56</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7.55 ± 13.20</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>557.73 ± 434.06</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>706.25 ± 404.58</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>49.77 ± 53.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>494.79 ± 419.61</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.60 ± 3.35</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>654.19 ± 430.63</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>796.55 ± 351.19</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>65.27 ± 65.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>510.00 ± 435.67</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5.55 ± 9.41</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>621.40 ± 436.57</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>685.27 ± 391.27</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>49.27 ± 49.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>393.28 ± 409.68</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>9.43 ± 42.61</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>654.30 ± 431.59</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>746.44 ± 357.06</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>57.30 ± 56.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>474.65 ± 426.23</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2.12 ± 4.43</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>607.67 ± 437.24</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>707.48 ± 384.83</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>50.11 ± 52.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>473.20 ± 431.37</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10.26 ± 19.18</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>664.14 ± 416.79</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>717.95 ± 392.54</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>51.78 ± 58.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>493.73 ± 449.01</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10.29 ± 17.52</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>597.00 ± 443.11</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>694.41 ± 389.46</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>45.99 ± 48.76</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Constraint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>297.31 ± 299.26</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.60 ± 4.73</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>577.55 ± 340.68</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16.87 ± 41.97</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>631.62 ± 269.68</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>50.91 ± 49.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>575.11 ± 343.32</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10.46 ± 23.57</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>551.85 ± 354.20</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>11.88 ± 31.65</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>647.15 ± 267.00</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>51.34 ± 52.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>263.60 ± 289.91</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5.94 ± 15.24</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>552.19 ± 350.51</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>12.04 ± 30.08</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>623.19 ± 268.87</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>49.97 ± 47.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>316.76 ± 299.90</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2.89 ± 6.39</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>550.43 ± 355.17</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>11.13 ± 27.23</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>636.22 ± 264.88</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>49.70 ± 50.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>591.21 ± 335.71</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10.10 ± 34.93</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>567.51 ± 346.57</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>9.77 ± 22.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>635.69 ± 264.75</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>49.79 ± 49.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>323.08 ± 309.17</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4.65 ± 11.15</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>591.27 ± 336.18</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>13.54 ± 34.50</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>646.55 ± 255.85</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>51.85 ± 51.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>341.92 ± 314.24</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10.02 ± 23.69</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>571.21 ± 345.54</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>14.23 ± 32.97</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>653.95 ± 262.15</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>54.32 ± 54.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>588.18 ± 339.31</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>18.51 ± 42.11</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>570.17 ± 345.69</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>14.72 ± 35.10</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>632.10 ± 265.75</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>51.22 ± 52.89</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Constraint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>320.19 ± 199.54</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.06 ± 3.74</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>329.54 ± 206.74</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>6.71 ± 21.11</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>417.05 ± 154.73</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>47.11 ± 43.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>315.50 ± 199.89</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3.70 ± 15.28</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>341.76 ± 208.01</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6.82 ± 19.93</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>417.78 ± 156.17</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>50.91 ± 51.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>332.84 ± 203.64</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>340.32 ± 203.02</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6.21 ± 13.61</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>420.68 ± 151.11</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>51.19 ± 47.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>292.21 ± 203.15</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8.05 ± 14.83</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>337.39 ± 205.18</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7.94 ± 25.48</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>422.11 ± 152.57</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>52.42 ± 48.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>271.05 ± 198.81</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.27 ± 1.50</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>331.89 ± 209.86</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7.45 ± 21.91</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>419.68 ± 152.74</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>48.45 ± 47.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>324.22 ± 202.06</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.41 ± 7.39</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>316.40 ± 209.66</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5.52 ± 11.81</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>415.07 ± 155.81</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>51.87 ± 48.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>315.81 ± 210.55</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10.09 ± 19.52</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>335.61 ± 209.04</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5.73 ± 15.10</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>420.85 ± 148.05</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>52.99 ± 50.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>341.12 ± 199.66</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10.50 ± 31.75</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>347.17 ± 201.38</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6.71 ± 17.31</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>422.56 ± 148.88</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>48.20 ± 44.02</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Constraint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>328.81 ± 403.57</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.21</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>339.89 ± 407.49</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>722.73 ± 458.21</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>70.86 ± 73.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>373.08 ± 421.81</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.12 ± 0.65</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>345.91 ± 429.18</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.36</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>763.98 ± 459.96</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>69.32 ± 68.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>345.00 ± 412.82</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>344.35 ± 415.62</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.27</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>771.57 ± 463.23</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>72.01 ± 75.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>386.29 ± 427.35</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3.92 ± 11.04</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>325.74 ± 403.39</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.19</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>757.61 ± 462.99</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>74.45 ± 79.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>379.87 ± 428.50</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.73 ± 5.68</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>346.27 ± 419.56</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>736.01 ± 455.12</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>67.50 ± 69.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>366.37 ± 416.94</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.89 ± 3.28</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>357.61 ± 419.30</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.27</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>785.39 ± 443.48</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>72.95 ± 72.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>348.52 ± 406.50</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.29 ± 5.87</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>321.93 ± 395.85</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.08</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>759.47 ± 453.97</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>75.00 ± 73.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>345.53 ± 412.91</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.30 ± 1.47</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>334.11 ± 400.30</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>794.73 ± 438.57</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>78.88 ± 72.14</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Constraint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>480.78 ± 376.58</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6.67 ± 17.91</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>287.23 ± 320.33</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3.44 ± 10.79</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>580.17 ± 285.76</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>51.05 ± 53.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>489.65 ± 376.82</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>11.75 ± 33.64</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>276.42 ± 310.85</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3.17 ± 9.21</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>560.85 ± 292.65</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>47.72 ± 48.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>503.01 ± 373.26</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7.67 ± 21.57</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>279.96 ± 320.22</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3.67 ± 16.24</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>604.66 ± 279.99</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>47.37 ± 47.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>289.22 ± 322.74</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>9.68 ± 20.88</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>276.99 ± 313.49</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2.78 ± 11.62</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>589.17 ± 284.54</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>50.38 ± 51.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>395.36 ± 363.25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12.43 ± 27.90</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>298.98 ± 319.03</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.29 ± 11.47</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>598.58 ± 273.52</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>49.76 ± 47.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>300.56 ± 327.36</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7.10 ± 24.62</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>283.77 ± 315.81</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3.29 ± 11.84</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>593.63 ± 280.88</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>48.95 ± 49.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>267.58 ± 304.17</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3.89 ± 10.18</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>288.40 ± 318.79</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.48 ± 12.28</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>575.48 ± 292.35</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>46.55 ± 49.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>516.10 ± 365.31</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10.39 ± 31.41</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>300.56 ± 325.01</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.33 ± 9.53</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>577.67 ± 293.82</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>48.39 ± 52.28</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Constraint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>478.03 ± 435.42</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>27.61 ± 75.33</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>560.00 ± 442.82</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16.88 ± 50.48</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>695.65 ± 397.70</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>33.54 ± 71.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>475.67 ± 424.98</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>17.85 ± 66.22</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>543.76 ± 445.37</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>13.04 ± 38.11</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>675.08 ± 403.57</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>30.38 ± 63.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>478.95 ± 436.48</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>29.23 ± 111.28</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>532.65 ± 450.82</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>20.19 ± 60.78</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>686.90 ± 399.59</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>35.62 ± 80.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>514.73 ± 431.98</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>17.36 ± 73.38</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>572.14 ± 448.44</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>24.44 ± 74.53</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>699.81 ± 395.94</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>39.12 ± 79.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>546.35 ± 447.58</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>16.98 ± 73.16</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>537.82 ± 449.32</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>21.47 ± 69.87</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>715.78 ± 387.27</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>33.50 ± 69.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>625.85 ± 438.62</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>16.37 ± 55.34</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>569.21 ± 442.37</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>17.91 ± 56.69</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>715.43 ± 392.19</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>39.85 ± 77.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>527.19 ± 437.89</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10.66 ± 38.67</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>565.13 ± 447.60</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>18.02 ± 62.97</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>713.95 ± 390.69</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>34.78 ± 72.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>615.11 ± 441.78</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>28.61 ± 114.62</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>568.65 ± 444.16</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>23.21 ± 59.84</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>707.87 ± 386.16</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>40.80 ± 87.47</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4368,4 +7505,451 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Constraint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>127.83 ± 123.41</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.11</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>132.30 ± 125.35</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>210.14 ± 110.00</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>40.38 ± 39.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>128.24 ± 123.30</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>121.54 ± 121.53</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.06</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>214.08 ± 106.31</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>41.34 ± 38.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>132.51 ± 127.14</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.09</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>125.31 ± 123.10</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.08</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>201.16 ± 111.33</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>40.12 ± 40.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>130.31 ± 122.76</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.19 ± 3.96</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>130.32 ± 123.25</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>214.59 ± 104.14</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>40.34 ± 39.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>115.89 ± 121.49</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.06 ± 1.07</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>118.43 ± 123.71</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>208.78 ± 111.26</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>39.37 ± 41.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>117.85 ± 121.42</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.16</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>117.53 ± 121.03</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.66</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>210.22 ± 108.99</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>37.56 ± 40.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>117.75 ± 121.17</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.21 ± 4.05</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>122.66 ± 121.74</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>208.81 ± 104.09</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>38.44 ± 39.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>116.28 ± 120.59</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.07 ± 0.74</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>118.79 ± 121.75</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.06</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>211.58 ± 105.75</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>39.72 ± 40.95</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crl_summary_results.xlsx
+++ b/crl_summary_results.xlsx
@@ -926,7 +926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1359,6 +1359,53 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>25.40 ± 29.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>107.43 ± 111.02</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>96.00 ± 100.10</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>209.63 ± 109.21</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>21.72 ± 27.37</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1806,6 +1853,53 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>45.99 ± 48.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>400.00 ± 396.06</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7.20 ± 10.55</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>640.76 ± 428.44</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>773.75 ± 369.01</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>54.18 ± 54.64</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2253,6 +2347,53 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>51.22 ± 52.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>595.59 ± 332.24</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>16.01 ± 47.08</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>562.31 ± 349.91</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>13.57 ± 30.51</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>649.06 ± 252.34</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>55.14 ± 55.05</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3147,6 +3288,53 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>78.88 ± 72.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>365.89 ± 410.42</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4.76 ± 12.73</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>338.35 ± 414.85</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>772.98 ± 450.03</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>71.78 ± 71.30</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3594,6 +3782,53 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>48.39 ± 52.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>479.64 ± 376.24</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>12.68 ± 44.28</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>276.94 ± 317.47</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3.24 ± 11.18</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>600.65 ± 283.72</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>51.99 ± 57.06</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3677,41 +3912,41 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>478.03 ± 435.42</t>
+          <t>83.00 ± 125.57</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>27.61 ± 75.33</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>560.00 ± 442.82</t>
+          <t>84.50 ± 125.10</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16.88 ± 50.48</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>695.65 ± 397.70</t>
+          <t>184.75 ± 124.47</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>33.54 ± 71.60</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -3724,41 +3959,41 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>475.67 ± 424.98</t>
+          <t>156.00 ± 86.09</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17.85 ± 66.22</t>
+          <t>1.75 ± 3.03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>543.76 ± 445.37</t>
+          <t>214.25 ± 123.91</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>13.04 ± 38.11</t>
+          <t>12.25 ± 21.22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>675.08 ± 403.57</t>
+          <t>156.75 ± 143.38</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>30.38 ± 63.54</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -3771,41 +4006,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>478.95 ± 436.48</t>
+          <t>157.25 ± 142.88</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.64</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>29.23 ± 111.28</t>
+          <t>38.75 ± 67.12</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>532.65 ± 450.82</t>
+          <t>159.75 ± 140.25</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>20.19 ± 60.78</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>686.90 ± 399.59</t>
+          <t>192.25 ± 110.17</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>35.62 ± 80.03</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -3818,41 +4053,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>514.73 ± 431.98</t>
+          <t>238.75 ± 106.09</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.62</v>
+        <v>0.25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.36 ± 73.38</t>
+          <t>4.00 ± 6.93</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>572.14 ± 448.44</t>
+          <t>228.00 ± 124.71</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.53</v>
+        <v>0.25</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>24.44 ± 74.53</t>
+          <t>0.75 ± 1.30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>699.81 ± 395.94</t>
+          <t>230.00 ± 121.24</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>39.12 ± 79.58</t>
+          <t>1.00 ± 1.73</t>
         </is>
       </c>
     </row>
@@ -3865,41 +4100,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>546.35 ± 447.58</t>
+          <t>259.00 ± 71.01</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16.98 ± 73.16</t>
+          <t>6.25 ± 7.46</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>537.82 ± 449.32</t>
+          <t>231.75 ± 118.21</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.47 ± 69.87</t>
+          <t>2.00 ± 2.45</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>715.78 ± 387.27</t>
+          <t>228.50 ± 71.59</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>33.50 ± 69.01</t>
+          <t>11.50 ± 7.83</t>
         </is>
       </c>
     </row>
@@ -3912,41 +4147,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>625.85 ± 438.62</t>
+          <t>225.75 ± 128.60</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.47</v>
+        <v>0.25</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.37 ± 55.34</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>569.21 ± 442.37</t>
+          <t>225.75 ± 128.60</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.54</v>
+        <v>0.25</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>17.91 ± 56.69</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>715.43 ± 392.19</t>
+          <t>234.25 ± 113.88</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>39.85 ± 77.72</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -3959,41 +4194,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>527.19 ± 437.89</t>
+          <t>212.75 ± 122.45</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.66 ± 38.67</t>
+          <t>1.50 ± 2.60</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>565.13 ± 447.60</t>
+          <t>132.50 ± 96.76</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.52</v>
+        <v>0.75</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>18.02 ± 62.97</t>
+          <t>4.00 ± 6.93</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>713.95 ± 390.69</t>
+          <t>255.25 ± 77.51</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.41</v>
+        <v>0.25</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>34.78 ± 72.80</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -4006,41 +4241,88 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>615.11 ± 441.78</t>
+          <t>226.00 ± 128.17</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.47</v>
+        <v>0.25</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28.61 ± 114.62</t>
+          <t>8.75 ± 15.16</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>568.65 ± 444.16</t>
+          <t>217.50 ± 116.34</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>23.21 ± 59.84</t>
+          <t>1.75 ± 3.03</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>707.87 ± 386.16</t>
+          <t>242.50 ± 99.59</t>
         </is>
       </c>
       <c r="J9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>22.00 ± 22.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>562.10 ± 433.08</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>13.96 ± 44.98</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>556.30 ± 440.38</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>17.43 ± 54.49</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>709.87 ± 387.64</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>0.42</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>40.80 ± 87.47</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>38.47 ± 83.72</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7949,6 +8231,53 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>137.37 ± 128.78</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.12</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>126.72 ± 123.55</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.41</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>212.43 ± 107.28</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>42.74 ± 42.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
